--- a/hw5b/hw5b-excel.xlsx
+++ b/hw5b/hw5b-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learning-area\uit-msc\subjects\phan-tich-du-lieu-kinh-doanh\assignments\hw5b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68905BB7-D4C4-4336-A447-644721B2403A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D5F8A3-665E-4B29-B8E4-8B3C68A1F88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9900" yWindow="-18270" windowWidth="21730" windowHeight="15410" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11390" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>Date</t>
   </si>
@@ -60,9 +60,6 @@
     <t>dy</t>
   </si>
   <si>
-    <t>x_i = dy_lag1</t>
-  </si>
-  <si>
     <t>dy_pred</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
   </si>
   <si>
     <t>e=dy - dy_pred</t>
-  </si>
-  <si>
-    <t>x=e_lag1</t>
   </si>
   <si>
     <t>MA(1)</t>
@@ -321,23 +315,55 @@
     <t>Bước 5: dự báo với ARIMA(1,1,1)</t>
   </si>
   <si>
-    <t>dy(t+1) = beta_0 + beta_1*dt(t) + theta_0 + theta_1*e(t)</t>
-  </si>
-  <si>
     <t>y(t+1) = y(t) + dy(t+1)</t>
+  </si>
+  <si>
+    <t>y_lag1</t>
+  </si>
+  <si>
+    <t>dy_lag1</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>beta_0</t>
+  </si>
+  <si>
+    <t>beta_1</t>
+  </si>
+  <si>
+    <t>theta_0</t>
+  </si>
+  <si>
+    <t>theta_1</t>
+  </si>
+  <si>
+    <t>e_lag1</t>
+  </si>
+  <si>
+    <t>dy(t+1) = beta_0 + beta_1*dy(t) + theta_0 + theta_1*e(t)</t>
+  </si>
+  <si>
+    <t>mean(y)</t>
+  </si>
+  <si>
+    <t>y(t+1) = mean + beta_1*dy(t) + theta_1*e(t)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,20 +417,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFCCCCCC"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF7030A0"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,6 +446,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -480,7 +512,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -489,8 +521,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -501,32 +546,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -545,20 +578,1864 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y=Price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$C$4:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>60.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>56.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>55.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>56.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>56.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>56.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>56.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>56.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>56.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>58.3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>57.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>57.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB06-4AA4-BF98-E9B5149ECF91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="9903775"/>
+        <c:axId val="9899935"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="9903775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9899935"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="9899935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9903775"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>I(1) = dy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$E$5:$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6000000000000014</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8999999999999986</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.60000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.60000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.60000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.10000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.70000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.39999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.10000000000000142</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.10000000000000142</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-84D9-4693-B164-956FE555C43D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="9910975"/>
+        <c:axId val="9910015"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="9910975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9910015"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="9910015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9910975"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>217805</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>116840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>522605</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>97790</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{357880B3-3C53-3E80-F7F9-DB747F8AAE2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>184785</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>489585</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CE52EDA-B0EE-5B3C-F19F-075E02983CB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>193040</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>162560</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>24130</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123191</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>225562</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>41579</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>682338</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>153671</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -581,8 +2458,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6739890" y="3883660"/>
-          <a:ext cx="4297182" cy="628319"/>
+          <a:off x="7383780" y="9044941"/>
+          <a:ext cx="3706208" cy="582930"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -593,23 +2470,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>585048</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>147320</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>416093</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>651</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>2902</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>34337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A5A7B9C-0113-9C79-1FD9-28711124DEB0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FF1412D-DB5C-C969-4500-18F0471EC4D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -625,52 +2502,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10179898" y="2934970"/>
-          <a:ext cx="6676345" cy="5440061"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>294942</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>52070</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>117192</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>155609</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC3DD15-1EB3-33CB-67C3-922CEFDF9A57}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17357392" y="5068570"/>
-          <a:ext cx="5918250" cy="5126389"/>
+          <a:off x="5626100" y="6934200"/>
+          <a:ext cx="7038702" cy="916987"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -945,26 +2778,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -974,8 +2828,33 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3">
+        <f>C5</f>
+        <v>60.5</v>
+      </c>
+      <c r="T3">
+        <f>D5</f>
+        <v>60.8</v>
+      </c>
+      <c r="V3">
+        <f>E6</f>
+        <v>-4</v>
+      </c>
+      <c r="W3">
+        <f>F6</f>
+        <v>-0.29999999999999716</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>45748</v>
       </c>
@@ -985,8 +2864,24 @@
       <c r="C4">
         <v>60.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="S4">
+        <f t="shared" ref="S4:S21" si="0">C6</f>
+        <v>56.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T21" si="1">D6</f>
+        <v>60.5</v>
+      </c>
+      <c r="V4">
+        <f>E7</f>
+        <v>2</v>
+      </c>
+      <c r="W4">
+        <f>F7</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>45749</v>
       </c>
@@ -996,8 +2891,32 @@
       <c r="C5">
         <v>60.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <f>C4</f>
+        <v>60.8</v>
+      </c>
+      <c r="E5">
+        <f>C5-C4</f>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>58.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="1"/>
+        <v>56.5</v>
+      </c>
+      <c r="V5">
+        <f>E8</f>
+        <v>-4</v>
+      </c>
+      <c r="W5">
+        <f>F8</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>45750</v>
       </c>
@@ -1007,8 +2926,36 @@
       <c r="C6">
         <v>56.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <f t="shared" ref="D6:D23" si="2">C5</f>
+        <v>60.5</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E23" si="3">C6-C5</f>
+        <v>-4</v>
+      </c>
+      <c r="F6">
+        <f>E5</f>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="0"/>
+        <v>54.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="1"/>
+        <v>58.5</v>
+      </c>
+      <c r="V6">
+        <f>E9</f>
+        <v>-2.5</v>
+      </c>
+      <c r="W6">
+        <f>F9</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>45751</v>
       </c>
@@ -1018,8 +2965,36 @@
       <c r="C7">
         <v>58.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>56.5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ref="F7:F23" si="4">E6</f>
+        <v>-4</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="1"/>
+        <v>54.5</v>
+      </c>
+      <c r="V7">
+        <f>E10</f>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="W7">
+        <f>F10</f>
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>45755</v>
       </c>
@@ -1029,8 +3004,36 @@
       <c r="C8">
         <v>54.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>58.5</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>55.6</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="V8">
+        <f>E11</f>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="W8">
+        <f>F11</f>
+        <v>3.6000000000000014</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>45756</v>
       </c>
@@ -1040,8 +3043,36 @@
       <c r="C9">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>54.5</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>-2.5</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="4"/>
+        <v>-4</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="0"/>
+        <v>57.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="1"/>
+        <v>55.6</v>
+      </c>
+      <c r="V9">
+        <f>E12</f>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="W9">
+        <f>F12</f>
+        <v>1.8999999999999986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>45757</v>
       </c>
@@ -1051,8 +3082,36 @@
       <c r="C10">
         <v>55.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="3"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="4"/>
+        <v>-2.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="0"/>
+        <v>56.9</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="1"/>
+        <v>57.5</v>
+      </c>
+      <c r="V10">
+        <f>E13</f>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="W10">
+        <f>F13</f>
+        <v>-0.60000000000000142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>45758</v>
       </c>
@@ -1062,8 +3121,36 @@
       <c r="C11">
         <v>57.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>55.6</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="3"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="4"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="0"/>
+        <v>56.3</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="1"/>
+        <v>56.9</v>
+      </c>
+      <c r="V11">
+        <f>E14</f>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="W11">
+        <f>F14</f>
+        <v>-0.60000000000000142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>45761</v>
       </c>
@@ -1073,8 +3160,36 @@
       <c r="C12">
         <v>56.9</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>57.5</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="4"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="1"/>
+        <v>56.3</v>
+      </c>
+      <c r="V12">
+        <f>E15</f>
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <f>F15</f>
+        <v>-0.29999999999999716</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>45762</v>
       </c>
@@ -1084,8 +3199,36 @@
       <c r="C13">
         <v>56.3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>56.9</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="V13">
+        <f>E16</f>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="W13">
+        <f>F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>45763</v>
       </c>
@@ -1095,8 +3238,36 @@
       <c r="C14">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>56.3</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="4"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="0"/>
+        <v>56.6</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="V14">
+        <f>E17</f>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="W14">
+        <f>F17</f>
+        <v>0.60000000000000142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>45764</v>
       </c>
@@ -1106,8 +3277,36 @@
       <c r="C15">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="4"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="0"/>
+        <v>56.7</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>56.6</v>
+      </c>
+      <c r="V15">
+        <f>E18</f>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="W15">
+        <f>F18</f>
+        <v>0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>45765</v>
       </c>
@@ -1117,8 +3316,36 @@
       <c r="C16">
         <v>56.6</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="3"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="1"/>
+        <v>56.7</v>
+      </c>
+      <c r="V16">
+        <f>E19</f>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="W16">
+        <f>F19</f>
+        <v>-0.70000000000000284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>45768</v>
       </c>
@@ -1128,8 +3355,36 @@
       <c r="C17">
         <v>56.7</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>56.6</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="3"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="4"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="0"/>
+        <v>56.4</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="V17">
+        <f>E20</f>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="W17">
+        <f>F20</f>
+        <v>0.39999999999999858</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>45769</v>
       </c>
@@ -1139,8 +3394,36 @@
       <c r="C18">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>56.7</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="3"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="4"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="0"/>
+        <v>56.3</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="1"/>
+        <v>56.4</v>
+      </c>
+      <c r="V18">
+        <f>E21</f>
+        <v>2</v>
+      </c>
+      <c r="W18">
+        <f>F21</f>
+        <v>-0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>45770</v>
       </c>
@@ -1150,8 +3433,36 @@
       <c r="C19">
         <v>56.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="3"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="4"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="0"/>
+        <v>58.3</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="1"/>
+        <v>56.3</v>
+      </c>
+      <c r="V19">
+        <f>E22</f>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="W19">
+        <f>F22</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>45771</v>
       </c>
@@ -1161,8 +3472,36 @@
       <c r="C20">
         <v>56.3</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>56.4</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="3"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="4"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="0"/>
+        <v>57.5</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="1"/>
+        <v>58.3</v>
+      </c>
+      <c r="V20">
+        <f>E23</f>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="W20">
+        <f>F23</f>
+        <v>-0.79999999999999716</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>45772</v>
       </c>
@@ -1172,8 +3511,28 @@
       <c r="C21">
         <v>58.3</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>56.3</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="4"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="0"/>
+        <v>57.6</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="1"/>
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>45775</v>
       </c>
@@ -1183,8 +3542,20 @@
       <c r="C22">
         <v>57.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>58.3</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="3"/>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>45776</v>
       </c>
@@ -1193,6 +3564,18 @@
       </c>
       <c r="C23">
         <v>57.6</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>57.5</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="3"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="4"/>
+        <v>-0.79999999999999716</v>
       </c>
     </row>
   </sheetData>
@@ -1200,26 +3583,28 @@
     <hyperlink ref="B2" r:id="rId1" xr:uid="{65E28EA4-3B46-4091-BF7F-F9D2EB633DF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED414EFB-4F8C-42FE-BE42-13B8FE7FA492}">
-  <dimension ref="A1:AF48"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" customWidth="1"/>
-    <col min="20" max="20" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.21875" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="5.21875" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1229,1017 +3614,1201 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="7"/>
+      <c r="E1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="13"/>
       <c r="H1" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I1" s="14"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <f>data!A4</f>
         <v>45748</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <f>data!B4</f>
         <v>1</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="11">
         <f>data!C4</f>
         <v>60.8</v>
       </c>
-      <c r="D2" s="6"/>
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" t="s">
         <v>9</v>
       </c>
-      <c r="S2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF2" s="15">
-        <v>-0.19026352121976101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>data!A5</f>
         <v>45749</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <f>data!B5</f>
         <v>2</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="11">
         <f>data!C5</f>
         <v>60.5</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="23">
+      <c r="E3" s="9">
         <f>C3-C2</f>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
+      <c r="F3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF3" s="16">
-        <v>-0.15901314604718178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <f>data!A6</f>
         <v>45750</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <f>data!B6</f>
         <v>3</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="11">
         <f>data!C6</f>
         <v>56.5</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="23">
+      <c r="E4" s="9">
         <f>C4-C3</f>
         <v>-4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="9">
         <f>E3</f>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="G4" s="13">
-        <f>$AF$2+$AF$3*F4</f>
+      <c r="G4" s="7">
+        <f>$L$9+$M$9*F4</f>
         <v>-0.14255957740560693</v>
       </c>
-      <c r="H4">
-        <f>E4-F4</f>
-        <v>-3.7000000000000028</v>
-      </c>
-      <c r="K4" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="T4" s="11"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="H4" s="7">
+        <f>E4-G4</f>
+        <v>-3.8574404225943932</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S4" s="18"/>
+      <c r="U4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <f>data!A7</f>
         <v>45751</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <f>data!B7</f>
         <v>4</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="11">
         <f>data!C7</f>
         <v>58.5</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5">
-        <f t="shared" ref="E4:E21" si="0">C5-C4</f>
+      <c r="E5" s="9">
+        <f t="shared" ref="E5:E25" si="0">C5-C4</f>
         <v>2</v>
       </c>
-      <c r="F5">
-        <f t="shared" ref="F5:F21" si="1">E4</f>
+      <c r="F5" s="9">
+        <f t="shared" ref="F5:F25" si="1">E4</f>
         <v>-4</v>
       </c>
-      <c r="G5" s="13">
-        <f>$AF$2+$AF$3*F5</f>
+      <c r="G5" s="7">
+        <f>$L$9+$M$9*F5</f>
         <v>0.44578906296896614</v>
       </c>
-      <c r="H5">
-        <f t="shared" ref="H5:H21" si="2">E5-F5</f>
-        <v>6</v>
+      <c r="H5" s="7">
+        <f t="shared" ref="H5:H22" si="2">E5-G5</f>
+        <v>1.554210937031034</v>
       </c>
       <c r="I5">
         <f>H4</f>
-        <v>-3.7000000000000028</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="T5" s="8">
+        <v>-3.8574404225943932</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="S5" s="15">
         <v>0.15894228639215383</v>
       </c>
-      <c r="AE5" s="30"/>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="U5" s="17"/>
+      <c r="V5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="W5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="X5" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z5" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <f>data!A8</f>
         <v>45755</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <f>data!B8</f>
         <v>5</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="11">
         <f>data!C8</f>
         <v>54.5</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>-4</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G6" s="13">
-        <f>$AF$2+$AF$3*F6</f>
+      <c r="G6" s="7">
+        <f>$L$9+$M$9*F6</f>
         <v>-0.50828981331412459</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="7">
         <f t="shared" si="2"/>
-        <v>-6</v>
+        <v>-3.4917101866858755</v>
       </c>
       <c r="I6">
         <f t="shared" ref="I6:I21" si="3">H5</f>
-        <v>6</v>
-      </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="T6" s="8">
+        <v>1.554210937031034</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="S6" s="15">
         <v>2.5262650403565446E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="U6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="V6" s="15">
+        <v>1</v>
+      </c>
+      <c r="W6" s="15">
+        <v>1.6381004261960825</v>
+      </c>
+      <c r="X6" s="15">
+        <v>1.6381004261960825</v>
+      </c>
+      <c r="Y6" s="15">
+        <v>0.41467827884547254</v>
+      </c>
+      <c r="Z6" s="15">
+        <v>0.5287282593471323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <f>data!A9</f>
         <v>45756</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <f>data!B9</f>
         <v>6</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="11">
         <f>data!C9</f>
         <v>52</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>-2.5</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="G7" s="13">
-        <f>$AF$2+$AF$3*F7</f>
+      <c r="G7" s="7">
+        <f>$L$9+$M$9*F7</f>
         <v>0.44578906296896614</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="7">
         <f t="shared" si="2"/>
-        <v>1.5</v>
+        <v>-2.945789062968966</v>
       </c>
       <c r="I7">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>-3.4917101866858755</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="T7" s="8">
+        <v>41</v>
+      </c>
+      <c r="R7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="15">
         <v>-3.5658433946211709E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="U7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="15">
+        <v>16</v>
+      </c>
+      <c r="W7" s="15">
+        <v>63.204677351581701</v>
+      </c>
+      <c r="X7" s="15">
+        <v>3.9502923344738563</v>
+      </c>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+    </row>
+    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <f>data!A10</f>
         <v>45757</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <f>data!B10</f>
         <v>7</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="11">
         <f>data!C10</f>
         <v>55.6</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8">
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>3.6000000000000014</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>-2.5</v>
       </c>
-      <c r="G8" s="13">
-        <f>$AF$2+$AF$3*F8</f>
+      <c r="G8" s="7">
+        <f>$L$9+$M$9*F8</f>
         <v>0.20726934389819343</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="7">
         <f t="shared" si="2"/>
-        <v>6.1000000000000014</v>
+        <v>3.3927306561018078</v>
       </c>
       <c r="I8">
         <f t="shared" si="3"/>
-        <v>1.5</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="T8" s="8">
+        <v>-2.945789062968966</v>
+      </c>
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="S8" s="15">
         <v>1.9875342347929146</v>
       </c>
-      <c r="AF8" s="17">
-        <v>0.2264997677220224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" s="16">
+        <v>17</v>
+      </c>
+      <c r="W8" s="16">
+        <v>64.842777777777783</v>
+      </c>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+    </row>
+    <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <f>data!A11</f>
         <v>45758</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <f>data!B11</f>
         <v>8</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="11">
         <f>data!C11</f>
         <v>57.5</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9">
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>1.8999999999999986</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="9">
         <f t="shared" si="1"/>
         <v>3.6000000000000014</v>
       </c>
-      <c r="G9" s="13">
-        <f>$AF$2+$AF$3*F9</f>
+      <c r="G9" s="7">
+        <f>$L$9+$M$9*F9</f>
         <v>-0.76271084698961567</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="7">
         <f t="shared" si="2"/>
-        <v>-1.7000000000000028</v>
+        <v>2.6627108469896141</v>
       </c>
       <c r="I9">
         <f t="shared" si="3"/>
-        <v>6.1000000000000014</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="T9" s="9">
+        <v>3.3927306561018078</v>
+      </c>
+      <c r="L9" s="23">
+        <f>S12</f>
+        <v>-0.19026352121976101</v>
+      </c>
+      <c r="M9" s="24">
+        <f>S13</f>
+        <v>-0.15901314604718178</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="S9" s="16">
         <v>18</v>
       </c>
-      <c r="AF9" s="18">
-        <v>-0.49900789745124108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <f>data!A12</f>
         <v>45761</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <f>data!B12</f>
         <v>9</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="11">
         <f>data!C12</f>
         <v>56.9</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>-0.60000000000000142</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>1.8999999999999986</v>
       </c>
-      <c r="G10" s="13">
-        <f>$AF$2+$AF$3*F10</f>
+      <c r="G10" s="7">
+        <f>$L$9+$M$9*F10</f>
         <v>-0.49238849870940615</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="7">
         <f t="shared" si="2"/>
-        <v>-2.5</v>
+        <v>-0.10761150129059527</v>
       </c>
       <c r="I10">
         <f t="shared" si="3"/>
-        <v>-1.7000000000000028</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2.6627108469896141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <f>data!A13</f>
         <v>45762</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <f>data!B13</f>
         <v>10</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="11">
         <f>data!C13</f>
         <v>56.3</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>-0.60000000000000142</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>-0.60000000000000142</v>
       </c>
-      <c r="G11" s="13">
-        <f>$AF$2+$AF$3*F11</f>
+      <c r="G11" s="7">
+        <f>$L$9+$M$9*F11</f>
         <v>-9.4855633591451716E-2</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.50514436640854976</v>
       </c>
       <c r="I11">
         <f t="shared" si="3"/>
-        <v>-2.5</v>
-      </c>
-      <c r="S11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+        <v>-0.10761150129059527</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="W11" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="X11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z11" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <f>data!A14</f>
         <v>45763</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12">
         <f>data!B14</f>
         <v>11</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="12">
         <f>data!C14</f>
         <v>56</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12">
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>-0.60000000000000142</v>
       </c>
-      <c r="G12" s="13">
-        <f>$AF$2+$AF$3*F12</f>
+      <c r="G12" s="7">
+        <f>$L$9+$M$9*F12</f>
         <v>-9.4855633591451716E-2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="7">
         <f t="shared" si="2"/>
-        <v>0.30000000000000426</v>
+        <v>-0.20514436640854544</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="V12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="W12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="X12" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+        <v>-0.50514436640854976</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="S12" s="21">
+        <v>-0.19026352121976101</v>
+      </c>
+      <c r="T12" s="15">
+        <v>0.47064863405240476</v>
+      </c>
+      <c r="U12" s="15">
+        <v>-0.40425809713191679</v>
+      </c>
+      <c r="V12" s="15">
+        <v>0.69137527969517887</v>
+      </c>
+      <c r="W12" s="15">
+        <v>-1.1879940546186991</v>
+      </c>
+      <c r="X12" s="15">
+        <v>0.80746701217917705</v>
+      </c>
+      <c r="Y12" s="15">
+        <v>-1.1879940546186991</v>
+      </c>
+      <c r="Z12" s="15">
+        <v>0.80746701217917705</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <f>data!A15</f>
         <v>45764</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13">
         <f>data!B15</f>
         <v>12</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="12">
         <f>data!C15</f>
         <v>56</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="G13" s="13">
-        <f>$AF$2+$AF$3*F13</f>
+      <c r="G13" s="7">
+        <f>$L$9+$M$9*F13</f>
         <v>-0.14255957740560693</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="7">
         <f t="shared" si="2"/>
-        <v>0.29999999999999716</v>
+        <v>0.14255957740560693</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>0.30000000000000426</v>
-      </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="T13" s="8">
-        <v>1</v>
-      </c>
-      <c r="U13" s="8">
-        <v>1.6381004261960825</v>
-      </c>
-      <c r="V13" s="8">
-        <v>1.6381004261960825</v>
-      </c>
-      <c r="W13" s="8">
-        <v>0.41467827884547254</v>
-      </c>
-      <c r="X13" s="8">
-        <v>0.5287282593471323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+        <v>-0.20514436640854544</v>
+      </c>
+      <c r="R13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="22">
+        <v>-0.15901314604718178</v>
+      </c>
+      <c r="T13" s="16">
+        <v>0.24693200711449162</v>
+      </c>
+      <c r="U13" s="16">
+        <v>-0.64395518387964301</v>
+      </c>
+      <c r="V13" s="16">
+        <v>0.52872825934713608</v>
+      </c>
+      <c r="W13" s="16">
+        <v>-0.68248561647653316</v>
+      </c>
+      <c r="X13" s="16">
+        <v>0.36445932438216966</v>
+      </c>
+      <c r="Y13" s="16">
+        <v>-0.68248561647653316</v>
+      </c>
+      <c r="Z13" s="16">
+        <v>0.36445932438216966</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <f>data!A16</f>
         <v>45765</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14">
         <f>data!B16</f>
         <v>13</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="12">
         <f>data!C16</f>
         <v>56.6</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14">
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>0.60000000000000142</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="13">
-        <f>$AF$2+$AF$3*F14</f>
+      <c r="G14" s="7">
+        <f>$L$9+$M$9*F14</f>
         <v>-0.19026352121976101</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="7">
         <f t="shared" si="2"/>
-        <v>0.60000000000000142</v>
+        <v>0.7902635212197624</v>
       </c>
       <c r="I14">
         <f t="shared" si="3"/>
-        <v>0.29999999999999716</v>
-      </c>
-      <c r="K14" t="s">
-        <v>49</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T14" s="8">
-        <v>16</v>
-      </c>
-      <c r="U14" s="8">
-        <v>63.204677351581701</v>
-      </c>
-      <c r="V14" s="8">
-        <v>3.9502923344738563</v>
-      </c>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-    </row>
-    <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.14255957740560693</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <f>data!A17</f>
         <v>45768</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15">
         <f>data!B17</f>
         <v>14</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="12">
         <f>data!C17</f>
         <v>56.7</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>0.10000000000000142</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="9">
         <f t="shared" si="1"/>
         <v>0.60000000000000142</v>
       </c>
-      <c r="G15" s="13">
-        <f>$AF$2+$AF$3*F15</f>
+      <c r="G15" s="7">
+        <f>$L$9+$M$9*F15</f>
         <v>-0.2856714088480703</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="7">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0.38567140884807172</v>
       </c>
       <c r="I15">
         <f t="shared" si="3"/>
-        <v>0.60000000000000142</v>
+        <v>0.7902635212197624</v>
       </c>
       <c r="K15" t="s">
-        <v>50</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T15" s="9">
-        <v>17</v>
-      </c>
-      <c r="U15" s="9">
-        <v>64.842777777777783</v>
-      </c>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <f>data!A18</f>
         <v>45769</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16">
         <f>data!B18</f>
         <v>15</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="12">
         <f>data!C18</f>
         <v>56</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16">
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>-0.70000000000000284</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="9">
         <f t="shared" si="1"/>
         <v>0.10000000000000142</v>
       </c>
-      <c r="G16" s="13">
-        <f>$AF$2+$AF$3*F16</f>
+      <c r="G16" s="7">
+        <f>$L$9+$M$9*F16</f>
         <v>-0.20616483582447942</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="7">
         <f t="shared" si="2"/>
-        <v>-0.80000000000000426</v>
+        <v>-0.49383516417552342</v>
       </c>
       <c r="I16">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
+        <v>0.38567140884807172</v>
       </c>
       <c r="K16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <f>data!A19</f>
         <v>45770</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17">
         <f>data!B19</f>
         <v>16</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="12">
         <f>data!C19</f>
         <v>56.4</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>0.39999999999999858</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>-0.70000000000000284</v>
       </c>
-      <c r="G17" s="13">
-        <f>$AF$2+$AF$3*F17</f>
+      <c r="G17" s="7">
+        <f>$L$9+$M$9*F17</f>
         <v>-7.8954318986733302E-2</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="7">
         <f t="shared" si="2"/>
-        <v>1.1000000000000014</v>
+        <v>0.47895431898673191</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>-0.80000000000000426</v>
-      </c>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="U17" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V17" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="W17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="X17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA17" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+        <v>-0.49383516417552342</v>
+      </c>
+      <c r="K17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <f>data!A20</f>
         <v>45771</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18">
         <f>data!B20</f>
         <v>17</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="12">
         <f>data!C20</f>
         <v>56.3</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18">
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
         <v>-0.10000000000000142</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="9">
         <f t="shared" si="1"/>
         <v>0.39999999999999858</v>
       </c>
-      <c r="G18" s="13">
-        <f>$AF$2+$AF$3*F18</f>
+      <c r="G18" s="7">
+        <f>$L$9+$M$9*F18</f>
         <v>-0.25386877963863352</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="7">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
+        <v>0.1538687796386321</v>
       </c>
       <c r="I18">
         <f t="shared" si="3"/>
-        <v>1.1000000000000014</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="U18" s="8">
-        <v>0.47064863405240476</v>
-      </c>
-      <c r="V18" s="8">
-        <v>-0.40425809713191679</v>
-      </c>
-      <c r="W18" s="8">
-        <v>0.69137527969517887</v>
-      </c>
-      <c r="X18" s="8">
-        <v>-1.1879940546186991</v>
-      </c>
-      <c r="Y18" s="8">
-        <v>0.80746701217917705</v>
-      </c>
-      <c r="Z18" s="8">
-        <v>-1.1879940546186991</v>
-      </c>
-      <c r="AA18" s="8">
-        <v>0.80746701217917705</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.47895431898673191</v>
+      </c>
+      <c r="K18" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" t="s">
+        <v>58</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" s="18"/>
+      <c r="U18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <f>data!A21</f>
         <v>45772</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19">
         <f>data!B21</f>
         <v>18</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="12">
         <f>data!C21</f>
         <v>58.3</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19">
+      <c r="E19" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="9">
         <f t="shared" si="1"/>
         <v>-0.10000000000000142</v>
       </c>
-      <c r="G19" s="13">
-        <f>$AF$2+$AF$3*F19</f>
+      <c r="G19" s="7">
+        <f>$L$9+$M$9*F19</f>
         <v>-0.17436220661504259</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="7">
         <f t="shared" si="2"/>
-        <v>2.1000000000000014</v>
+        <v>2.1743622066150428</v>
       </c>
       <c r="I19">
         <f t="shared" si="3"/>
-        <v>-0.5</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="U19" s="9">
-        <v>0.24693200711449162</v>
-      </c>
-      <c r="V19" s="9">
-        <v>-0.64395518387964301</v>
-      </c>
-      <c r="W19" s="9">
-        <v>0.52872825934713608</v>
-      </c>
-      <c r="X19" s="9">
-        <v>-0.68248561647653316</v>
-      </c>
-      <c r="Y19" s="9">
-        <v>0.36445932438216966</v>
-      </c>
-      <c r="Z19" s="9">
-        <v>-0.68248561647653316</v>
-      </c>
-      <c r="AA19" s="9">
-        <v>0.36445932438216966</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+        <v>0.1538687796386321</v>
+      </c>
+      <c r="L19" s="25">
+        <f>S26</f>
+        <v>0.22652862003091939</v>
+      </c>
+      <c r="M19" s="26">
+        <f>S27</f>
+        <v>-3.9581497398492753E-2</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="S19" s="15">
+        <v>4.567242436591519E-2</v>
+      </c>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="W19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="X19" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y19" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z19" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <f>data!A22</f>
         <v>45775</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20">
         <f>data!B22</f>
         <v>19</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="12">
         <f>data!C22</f>
         <v>57.5</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20">
+      <c r="E20" s="9">
         <f t="shared" si="0"/>
         <v>-0.79999999999999716</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="9">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="G20" s="13">
-        <f>$AF$2+$AF$3*F20</f>
+      <c r="G20" s="7">
+        <f>$L$9+$M$9*F20</f>
         <v>-0.50828981331412459</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="7">
         <f t="shared" si="2"/>
-        <v>-2.7999999999999972</v>
+        <v>-0.29171018668587256</v>
       </c>
       <c r="I20">
         <f t="shared" si="3"/>
-        <v>2.1000000000000014</v>
-      </c>
-      <c r="K20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+        <v>2.1743622066150428</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="S20" s="15">
+        <v>2.0859703474602437E-3</v>
+      </c>
+      <c r="U20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="V20" s="15">
+        <v>1</v>
+      </c>
+      <c r="W20" s="15">
+        <v>9.8978345211307328E-2</v>
+      </c>
+      <c r="X20" s="15">
+        <v>9.8978345211307328E-2</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>3.1354960730232702E-2</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>0.86181963605752743</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <f>data!A23</f>
         <v>45776</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21">
         <f>data!B23</f>
         <v>20</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="12">
         <f>data!C23</f>
         <v>57.6</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="22">
+      <c r="E21" s="9">
         <f t="shared" si="0"/>
         <v>0.10000000000000142</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="9">
         <f t="shared" si="1"/>
         <v>-0.79999999999999716</v>
       </c>
-      <c r="G21" s="13">
-        <f>$AF$2+$AF$3*F21</f>
+      <c r="G21" s="7">
+        <f>$L$9+$M$9*F21</f>
         <v>-6.3053004382016026E-2</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="7">
         <f t="shared" si="2"/>
-        <v>0.89999999999999858</v>
+        <v>0.16305300438201745</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>-2.7999999999999972</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="27">
+        <v>-0.29171018668587256</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="S21" s="15">
+        <v>-6.4441631629375745E-2</v>
+      </c>
+      <c r="U21" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="V21" s="15">
+        <v>15</v>
+      </c>
+      <c r="W21" s="15">
+        <v>47.35056729757197</v>
+      </c>
+      <c r="X21" s="15">
+        <v>3.1567044865047982</v>
+      </c>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+    </row>
+    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="31">
         <f>B21+1</f>
         <v>21</v>
       </c>
-      <c r="C22" s="25">
-        <f>C21+E22</f>
-        <v>57.134991577689163</v>
-      </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="25">
-        <f>$AF$3*E21+$AF$9*H21</f>
-        <v>-0.46500842231083467</v>
-      </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B23" s="27">
+      <c r="C22" s="32">
+        <f>$L$22+$M$9*E21+$M$19*H21</f>
+        <v>56.802644803326523</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29">
+        <f t="shared" si="0"/>
+        <v>-0.79735519667347887</v>
+      </c>
+      <c r="F22" s="30">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="G22" s="30">
+        <f>$L$9+$M$9*F22</f>
+        <v>-0.20616483582447942</v>
+      </c>
+      <c r="H22" s="30">
+        <f t="shared" si="2"/>
+        <v>-0.59119036084899945</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="27">
+        <f>AVERAGE(C2:D21)</f>
+        <v>56.825000000000003</v>
+      </c>
+      <c r="R22" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="S22" s="15">
+        <v>1.7767117060752422</v>
+      </c>
+      <c r="U22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="V22" s="16">
+        <v>16</v>
+      </c>
+      <c r="W22" s="16">
+        <v>47.449545642783278</v>
+      </c>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16"/>
+    </row>
+    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="31">
         <f t="shared" ref="B23:B25" si="4">B22+1</f>
         <v>22</v>
       </c>
-      <c r="C23" s="25">
-        <f t="shared" ref="C23:C25" si="5">C22+E23</f>
-        <v>57.245170276361506</v>
-      </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="25">
-        <f>$AF$2+$AF$3*E22+$AF$8+$AF$9*H22</f>
-        <v>0.11017869867234373</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="27">
+      <c r="C23" s="32">
+        <f t="shared" ref="C23:C25" si="5">$L$22+$M$9*E22+$M$19*H22</f>
+        <v>56.975190158070077</v>
+      </c>
+      <c r="D23" s="28"/>
+      <c r="E23" s="29">
+        <f t="shared" si="0"/>
+        <v>0.17254535474355492</v>
+      </c>
+      <c r="F23" s="30">
+        <f t="shared" si="1"/>
+        <v>-0.79735519667347887</v>
+      </c>
+      <c r="G23" s="30">
+        <f t="shared" ref="G23:G25" si="6">$L$9+$M$9*F23</f>
+        <v>-6.3473562879641759E-2</v>
+      </c>
+      <c r="H23" s="30">
+        <f t="shared" ref="H23:H25" si="7">E23-G23</f>
+        <v>0.23601891762319668</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="R23" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="S23" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="31">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="32">
         <f t="shared" si="5"/>
-        <v>57.263886661360495</v>
-      </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="25">
-        <f>$AF$2+$AF$3*E23+$AF$8+$AF$9*H23</f>
-        <v>1.8716384998987562E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="B25" s="27">
+        <v>56.788221038132505</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="29">
+        <f t="shared" si="0"/>
+        <v>-0.18696911993757226</v>
+      </c>
+      <c r="F24" s="30">
+        <f t="shared" si="1"/>
+        <v>0.17254535474355492</v>
+      </c>
+      <c r="G24" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.21770050091336068</v>
+      </c>
+      <c r="H24" s="30">
+        <f t="shared" si="7"/>
+        <v>3.0731380975788425E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B25" s="31">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="32">
         <f t="shared" si="5"/>
-        <v>57.297146756601435</v>
-      </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="25">
-        <f>$AF$2+$AF$3*E24+$AF$8+$AF$9*H24</f>
-        <v>3.3260095240942117E-2</v>
-      </c>
-      <c r="S25" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="T25" s="11"/>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="L26" s="13">
-        <v>0.41220000000000001</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="T26" s="8">
-        <v>0.52388658936948396</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+        <v>56.853514153898807</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29">
+        <f t="shared" si="0"/>
+        <v>6.5293115766301923E-2</v>
+      </c>
+      <c r="F25" s="30">
+        <f t="shared" si="1"/>
+        <v>-0.18696911993757226</v>
+      </c>
+      <c r="G25" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.16053297324481478</v>
+      </c>
+      <c r="H25" s="30">
+        <f t="shared" si="7"/>
+        <v>0.2258260890111167</v>
+      </c>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="V25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="W25" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="X25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y25" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z25" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="R26" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="S26" s="21">
+        <v>0.22652862003091939</v>
+      </c>
+      <c r="T26" s="15">
+        <v>0.4309212176479883</v>
+      </c>
+      <c r="U26" s="15">
+        <v>0.5256845352552737</v>
+      </c>
+      <c r="V26" s="15">
+        <v>0.60679213900757478</v>
+      </c>
+      <c r="W26" s="15">
+        <v>-0.69195821349694975</v>
+      </c>
+      <c r="X26" s="15">
+        <v>1.1450154535587886</v>
+      </c>
+      <c r="Y26" s="15">
+        <v>-0.69195821349694975</v>
+      </c>
+      <c r="Z26" s="15">
+        <v>1.1450154535587886</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>45776</v>
       </c>
@@ -2253,213 +4822,70 @@
         <v>0.100000000000001</v>
       </c>
       <c r="G27">
-        <f>E27*L26</f>
+        <f>E27*L35</f>
         <v>4.1220000000000416E-2</v>
       </c>
       <c r="H27">
         <f>E27-G27</f>
         <v>5.8780000000000589E-2</v>
       </c>
-      <c r="L27" s="13">
-        <v>-0.99950000000000006</v>
-      </c>
-      <c r="S27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="T27" s="8">
-        <v>0.27445715852119029</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="C28" s="21">
+      <c r="R27" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="S27" s="22">
+        <v>-3.9581497398492753E-2</v>
+      </c>
+      <c r="T27" s="16">
+        <v>0.22353168366373413</v>
+      </c>
+      <c r="U27" s="16">
+        <v>-0.17707332021010708</v>
+      </c>
+      <c r="V27" s="16">
+        <v>0.86181963605753087</v>
+      </c>
+      <c r="W27" s="16">
+        <v>-0.51602800296177009</v>
+      </c>
+      <c r="X27" s="16">
+        <v>0.43686500816478457</v>
+      </c>
+      <c r="Y27" s="16">
+        <v>-0.51602800296177009</v>
+      </c>
+      <c r="Z27" s="16">
+        <v>0.43686500816478457</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C28" s="9">
         <f>C27+E28</f>
         <v>57.58246939</v>
       </c>
-      <c r="E28" s="12">
-        <f>$L$26*E27+$L$27*H27</f>
+      <c r="E28" s="6">
+        <f>$L$35*E27+$L$36*H27</f>
         <v>-1.7530610000000175E-2</v>
       </c>
-      <c r="S28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="T28" s="8">
-        <v>0.22608763575593632</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="S29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="T29" s="8">
-        <v>2.5606697193075747</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="S30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="T30" s="9">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="S32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="19:27" x14ac:dyDescent="0.3">
-      <c r="S33" s="10"/>
-      <c r="T33" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="U33" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="V33" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="W33" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="X33" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="19:27" x14ac:dyDescent="0.3">
-      <c r="S34" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="T34" s="8">
-        <v>1</v>
-      </c>
-      <c r="U34" s="8">
-        <v>37.205735299907303</v>
-      </c>
-      <c r="V34" s="8">
-        <v>37.205735299907303</v>
-      </c>
-      <c r="W34" s="8">
-        <v>5.6741754483123676</v>
-      </c>
-      <c r="X34" s="8">
-        <v>3.0888671024197095E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="19:27" x14ac:dyDescent="0.3">
-      <c r="S35" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T35" s="8">
-        <v>15</v>
-      </c>
-      <c r="U35" s="8">
-        <v>98.35544117068099</v>
-      </c>
-      <c r="V35" s="8">
-        <v>6.5570294113787329</v>
-      </c>
-      <c r="W35" s="8"/>
-      <c r="X35" s="8"/>
-    </row>
-    <row r="36" spans="19:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="S36" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T36" s="9">
-        <v>16</v>
-      </c>
-      <c r="U36" s="9">
-        <v>135.56117647058829</v>
-      </c>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-    </row>
-    <row r="37" spans="19:27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="19:27" x14ac:dyDescent="0.3">
-      <c r="S38" s="10"/>
-      <c r="T38" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="U38" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V38" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="W38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="X38" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z38" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA38" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="19:27" x14ac:dyDescent="0.3">
-      <c r="S39" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="U39" s="8">
-        <v>0.62108419307286578</v>
-      </c>
-      <c r="V39" s="8">
-        <v>0.36468448279354193</v>
-      </c>
-      <c r="W39" s="8">
-        <v>0.72043723160537865</v>
-      </c>
-      <c r="X39" s="8">
-        <v>-1.0973098533574963</v>
-      </c>
-      <c r="Y39" s="8">
-        <v>1.5503093888015411</v>
-      </c>
-      <c r="Z39" s="8">
-        <v>-1.0973098533574963</v>
-      </c>
-      <c r="AA39" s="8">
-        <v>1.5503093888015411</v>
-      </c>
-    </row>
-    <row r="40" spans="19:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="S40" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="U40" s="9">
-        <v>0.20948649902736194</v>
-      </c>
-      <c r="V40" s="9">
-        <v>-2.3820527803372356</v>
-      </c>
-      <c r="W40" s="9">
-        <v>3.0888671024197248E-2</v>
-      </c>
-      <c r="X40" s="9">
-        <v>-0.94551780060401969</v>
-      </c>
-      <c r="Y40" s="9">
-        <v>-5.2497994298462414E-2</v>
-      </c>
-      <c r="Z40" s="9">
-        <v>-0.94551780060401969</v>
-      </c>
-      <c r="AA40" s="9">
-        <v>-5.2497994298462414E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="19:27" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="S44" s="31"/>
-    </row>
-    <row r="48" spans="19:27" x14ac:dyDescent="0.3">
-      <c r="U48" s="30"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="K30" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="K31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L35" s="7">
+        <v>0.41220000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L36" s="7">
+        <v>-0.99950000000000006</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/hw5b/hw5b-excel.xlsx
+++ b/hw5b/hw5b-excel.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learning-area\uit-msc\subjects\phan-tich-du-lieu-kinh-doanh\assignments\hw5b\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learning-area-main\mis-msc\semester\semester2\phan-tich-du-lieu-kinh-doanh\assignments\hw5b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D5F8A3-665E-4B29-B8E4-8B3C68A1F88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D514EF69-3986-4A5C-A8CF-66AB660961DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11390" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="arima" sheetId="2" r:id="rId2"/>
+    <sheet name="arima(1,1,1)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -353,6 +354,192 @@
   <si>
     <t>y(t+1) = mean + beta_1*dy(t) + theta_1*e(t)</t>
   </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ф</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ф</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>θ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>θ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Dự báo</t>
+  </si>
+  <si>
+    <t>dy(t) = y(t) - t(t-1)</t>
+  </si>
+  <si>
+    <t>y(t+1) = y(t) + dt(t+1)</t>
+  </si>
+  <si>
+    <r>
+      <t>dy(t+1) = Ф</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Ф</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*dy(t) + θ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+ θ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*e(t)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -361,9 +548,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +600,45 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -512,7 +738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -526,12 +752,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -546,20 +792,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2515,6 +2756,66 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C2A5383-450E-5960-0723-0ABF9E55A2F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7439025" y="2205037"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2779,14 +3080,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2797,7 +3098,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2818,7 +3119,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2846,15 +3147,15 @@
         <v>60.8</v>
       </c>
       <c r="V3">
-        <f>E6</f>
+        <f t="shared" ref="V3:V20" si="0">E6</f>
         <v>-4</v>
       </c>
       <c r="W3">
-        <f>F6</f>
+        <f t="shared" ref="W3:W20" si="1">F6</f>
         <v>-0.29999999999999716</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45748</v>
       </c>
@@ -2865,23 +3166,23 @@
         <v>60.8</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4:S21" si="0">C6</f>
+        <f t="shared" ref="S4:S21" si="2">C6</f>
         <v>56.5</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T21" si="1">D6</f>
+        <f t="shared" ref="T4:T21" si="3">D6</f>
         <v>60.5</v>
       </c>
       <c r="V4">
-        <f>E7</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="W4">
-        <f>F7</f>
+        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45749</v>
       </c>
@@ -2900,23 +3201,23 @@
         <v>-0.29999999999999716</v>
       </c>
       <c r="S5">
+        <f t="shared" si="2"/>
+        <v>58.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>56.5</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="0"/>
-        <v>58.5</v>
-      </c>
-      <c r="T5">
+        <v>-4</v>
+      </c>
+      <c r="W5">
         <f t="shared" si="1"/>
-        <v>56.5</v>
-      </c>
-      <c r="V5">
-        <f>E8</f>
-        <v>-4</v>
-      </c>
-      <c r="W5">
-        <f>F8</f>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45750</v>
       </c>
@@ -2927,11 +3228,11 @@
         <v>56.5</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6:D23" si="2">C5</f>
+        <f t="shared" ref="D6:D23" si="4">C5</f>
         <v>60.5</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E23" si="3">C6-C5</f>
+        <f t="shared" ref="E6:E23" si="5">C6-C5</f>
         <v>-4</v>
       </c>
       <c r="F6">
@@ -2939,23 +3240,23 @@
         <v>-0.29999999999999716</v>
       </c>
       <c r="S6">
+        <f t="shared" si="2"/>
+        <v>54.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>58.5</v>
+      </c>
+      <c r="V6">
         <f t="shared" si="0"/>
-        <v>54.5</v>
-      </c>
-      <c r="T6">
+        <v>-2.5</v>
+      </c>
+      <c r="W6">
         <f t="shared" si="1"/>
-        <v>58.5</v>
-      </c>
-      <c r="V6">
-        <f>E9</f>
-        <v>-2.5</v>
-      </c>
-      <c r="W6">
-        <f>F9</f>
         <v>-4</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>45751</v>
       </c>
@@ -2966,35 +3267,35 @@
         <v>58.5</v>
       </c>
       <c r="D7">
+        <f t="shared" si="4"/>
+        <v>56.5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ref="F7:F23" si="6">E6</f>
+        <v>-4</v>
+      </c>
+      <c r="S7">
         <f t="shared" si="2"/>
-        <v>56.5</v>
-      </c>
-      <c r="E7">
+        <v>52</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <f t="shared" ref="F7:F23" si="4">E6</f>
-        <v>-4</v>
-      </c>
-      <c r="S7">
+        <v>54.5</v>
+      </c>
+      <c r="V7">
         <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="T7">
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="W7">
         <f t="shared" si="1"/>
-        <v>54.5</v>
-      </c>
-      <c r="V7">
-        <f>E10</f>
-        <v>3.6000000000000014</v>
-      </c>
-      <c r="W7">
-        <f>F10</f>
         <v>-2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>45755</v>
       </c>
@@ -3005,35 +3306,35 @@
         <v>54.5</v>
       </c>
       <c r="D8">
+        <f t="shared" si="4"/>
+        <v>58.5</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="5"/>
+        <v>-4</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="2"/>
-        <v>58.5</v>
-      </c>
-      <c r="E8">
+        <v>55.6</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="3"/>
-        <v>-4</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="S8">
+        <v>52</v>
+      </c>
+      <c r="V8">
         <f t="shared" si="0"/>
-        <v>55.6</v>
-      </c>
-      <c r="T8">
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="W8">
         <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="V8">
-        <f>E11</f>
-        <v>1.8999999999999986</v>
-      </c>
-      <c r="W8">
-        <f>F11</f>
         <v>3.6000000000000014</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>45756</v>
       </c>
@@ -3044,35 +3345,35 @@
         <v>52</v>
       </c>
       <c r="D9">
+        <f t="shared" si="4"/>
+        <v>54.5</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="5"/>
+        <v>-2.5</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="6"/>
+        <v>-4</v>
+      </c>
+      <c r="S9">
         <f t="shared" si="2"/>
-        <v>54.5</v>
-      </c>
-      <c r="E9">
+        <v>57.5</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="3"/>
-        <v>-2.5</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="4"/>
-        <v>-4</v>
-      </c>
-      <c r="S9">
+        <v>55.6</v>
+      </c>
+      <c r="V9">
         <f t="shared" si="0"/>
-        <v>57.5</v>
-      </c>
-      <c r="T9">
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="W9">
         <f t="shared" si="1"/>
-        <v>55.6</v>
-      </c>
-      <c r="V9">
-        <f>E12</f>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="W9">
-        <f>F12</f>
         <v>1.8999999999999986</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>45757</v>
       </c>
@@ -3083,35 +3384,35 @@
         <v>55.6</v>
       </c>
       <c r="D10">
+        <f t="shared" si="4"/>
+        <v>52</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="5"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="6"/>
+        <v>-2.5</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="2"/>
-        <v>52</v>
-      </c>
-      <c r="E10">
+        <v>56.9</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="3"/>
-        <v>3.6000000000000014</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="4"/>
-        <v>-2.5</v>
-      </c>
-      <c r="S10">
+        <v>57.5</v>
+      </c>
+      <c r="V10">
         <f t="shared" si="0"/>
-        <v>56.9</v>
-      </c>
-      <c r="T10">
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="W10">
         <f t="shared" si="1"/>
-        <v>57.5</v>
-      </c>
-      <c r="V10">
-        <f>E13</f>
         <v>-0.60000000000000142</v>
       </c>
-      <c r="W10">
-        <f>F13</f>
-        <v>-0.60000000000000142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>45758</v>
       </c>
@@ -3122,35 +3423,35 @@
         <v>57.5</v>
       </c>
       <c r="D11">
+        <f t="shared" si="4"/>
+        <v>55.6</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="5"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="6"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="2"/>
-        <v>55.6</v>
-      </c>
-      <c r="E11">
+        <v>56.3</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="3"/>
-        <v>1.8999999999999986</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="4"/>
-        <v>3.6000000000000014</v>
-      </c>
-      <c r="S11">
+        <v>56.9</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="0"/>
-        <v>56.3</v>
-      </c>
-      <c r="T11">
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="W11">
         <f t="shared" si="1"/>
-        <v>56.9</v>
-      </c>
-      <c r="V11">
-        <f>E14</f>
-        <v>-0.29999999999999716</v>
-      </c>
-      <c r="W11">
-        <f>F14</f>
         <v>-0.60000000000000142</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>45761</v>
       </c>
@@ -3161,347 +3462,347 @@
         <v>56.9</v>
       </c>
       <c r="D12">
+        <f t="shared" si="4"/>
+        <v>57.5</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="5"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="6"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="3"/>
+        <v>56.3</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="1"/>
+        <v>-0.29999999999999716</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>45762</v>
+      </c>
+      <c r="B13" s="4">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>56.3</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="4"/>
+        <v>56.9</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="5"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="6"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>45763</v>
+      </c>
+      <c r="B14" s="4">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>56</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="4"/>
+        <v>56.3</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="5"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="6"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="2"/>
+        <v>56.6</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="0"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>45764</v>
+      </c>
+      <c r="B15" s="4">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>56</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="6"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="2"/>
+        <v>56.7</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="3"/>
+        <v>56.6</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="0"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>45765</v>
+      </c>
+      <c r="B16" s="4">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>56.6</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="5"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="3"/>
+        <v>56.7</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="0"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="1"/>
+        <v>-0.70000000000000284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>45768</v>
+      </c>
+      <c r="B17" s="4">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>56.7</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="4"/>
+        <v>56.6</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="5"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="6"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="2"/>
+        <v>56.4</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="0"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="1"/>
+        <v>0.39999999999999858</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>45769</v>
+      </c>
+      <c r="B18" s="4">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>56</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="4"/>
+        <v>56.7</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="5"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="6"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="2"/>
+        <v>56.3</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="3"/>
+        <v>56.4</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="1"/>
+        <v>-0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>45770</v>
+      </c>
+      <c r="B19" s="4">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>56.4</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="5"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="6"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="2"/>
+        <v>58.3</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="3"/>
+        <v>56.3</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="0"/>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>45771</v>
+      </c>
+      <c r="B20" s="4">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>56.3</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="4"/>
+        <v>56.4</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="5"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="6"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="S20">
         <f t="shared" si="2"/>
         <v>57.5</v>
       </c>
-      <c r="E12">
+      <c r="T20">
         <f t="shared" si="3"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="4"/>
-        <v>1.8999999999999986</v>
-      </c>
-      <c r="S12">
+        <v>58.3</v>
+      </c>
+      <c r="V20">
         <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="T12">
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="W20">
         <f t="shared" si="1"/>
-        <v>56.3</v>
-      </c>
-      <c r="V12">
-        <f>E15</f>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>F15</f>
-        <v>-0.29999999999999716</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>45762</v>
-      </c>
-      <c r="B13" s="4">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>56.3</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="2"/>
-        <v>56.9</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="3"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="4"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="V13">
-        <f>E16</f>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="W13">
-        <f>F16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>45763</v>
-      </c>
-      <c r="B14" s="4">
-        <v>11</v>
-      </c>
-      <c r="C14">
-        <v>56</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="2"/>
-        <v>56.3</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="3"/>
-        <v>-0.29999999999999716</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="4"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="0"/>
-        <v>56.6</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="V14">
-        <f>E17</f>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="W14">
-        <f>F17</f>
-        <v>0.60000000000000142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>45764</v>
-      </c>
-      <c r="B15" s="4">
-        <v>12</v>
-      </c>
-      <c r="C15">
-        <v>56</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="2"/>
-        <v>56</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="4"/>
-        <v>-0.29999999999999716</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>56.7</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
-        <v>56.6</v>
-      </c>
-      <c r="V15">
-        <f>E18</f>
-        <v>-0.70000000000000284</v>
-      </c>
-      <c r="W15">
-        <f>F18</f>
-        <v>0.10000000000000142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>45765</v>
-      </c>
-      <c r="B16" s="4">
-        <v>13</v>
-      </c>
-      <c r="C16">
-        <v>56.6</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="2"/>
-        <v>56</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="3"/>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="1"/>
-        <v>56.7</v>
-      </c>
-      <c r="V16">
-        <f>E19</f>
-        <v>0.39999999999999858</v>
-      </c>
-      <c r="W16">
-        <f>F19</f>
-        <v>-0.70000000000000284</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>45768</v>
-      </c>
-      <c r="B17" s="4">
-        <v>14</v>
-      </c>
-      <c r="C17">
-        <v>56.7</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="2"/>
-        <v>56.6</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="3"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="4"/>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="0"/>
-        <v>56.4</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="V17">
-        <f>E20</f>
-        <v>-0.10000000000000142</v>
-      </c>
-      <c r="W17">
-        <f>F20</f>
-        <v>0.39999999999999858</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>45769</v>
-      </c>
-      <c r="B18" s="4">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>56</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="2"/>
-        <v>56.7</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="3"/>
-        <v>-0.70000000000000284</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="4"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="0"/>
-        <v>56.3</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="1"/>
-        <v>56.4</v>
-      </c>
-      <c r="V18">
-        <f>E21</f>
-        <v>2</v>
-      </c>
-      <c r="W18">
-        <f>F21</f>
-        <v>-0.10000000000000142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>45770</v>
-      </c>
-      <c r="B19" s="4">
-        <v>16</v>
-      </c>
-      <c r="C19">
-        <v>56.4</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="2"/>
-        <v>56</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="3"/>
-        <v>0.39999999999999858</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="4"/>
-        <v>-0.70000000000000284</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="0"/>
-        <v>58.3</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="1"/>
-        <v>56.3</v>
-      </c>
-      <c r="V19">
-        <f>E22</f>
         <v>-0.79999999999999716</v>
       </c>
-      <c r="W19">
-        <f>F22</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>45771</v>
-      </c>
-      <c r="B20" s="4">
-        <v>17</v>
-      </c>
-      <c r="C20">
-        <v>56.3</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="2"/>
-        <v>56.4</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="3"/>
-        <v>-0.10000000000000142</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="4"/>
-        <v>0.39999999999999858</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="0"/>
-        <v>57.5</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="1"/>
-        <v>58.3</v>
-      </c>
-      <c r="V20">
-        <f>E23</f>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="W20">
-        <f>F23</f>
-        <v>-0.79999999999999716</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>45772</v>
       </c>
@@ -3512,27 +3813,27 @@
         <v>58.3</v>
       </c>
       <c r="D21">
+        <f t="shared" si="4"/>
+        <v>56.3</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="6"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="S21">
         <f t="shared" si="2"/>
-        <v>56.3</v>
-      </c>
-      <c r="E21">
+        <v>57.6</v>
+      </c>
+      <c r="T21">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="4"/>
-        <v>-0.10000000000000142</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
-        <v>57.6</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="1"/>
         <v>57.5</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>45775</v>
       </c>
@@ -3543,19 +3844,19 @@
         <v>57.5</v>
       </c>
       <c r="D22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>58.3</v>
       </c>
       <c r="E22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-0.79999999999999716</v>
       </c>
       <c r="F22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>45776</v>
       </c>
@@ -3566,15 +3867,15 @@
         <v>57.6</v>
       </c>
       <c r="D23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>57.5</v>
       </c>
       <c r="E23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.10000000000000142</v>
       </c>
       <c r="F23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-0.79999999999999716</v>
       </c>
     </row>
@@ -3590,21 +3891,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED414EFB-4F8C-42FE-BE42-13B8FE7FA492}">
   <dimension ref="A1:Z36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.21875" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="8.21875" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" customWidth="1"/>
-    <col min="10" max="10" width="5.21875" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="5.28515625" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3617,16 +3918,16 @@
       <c r="E1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="14"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="I1" s="30"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <f>data!A4</f>
         <v>45748</v>
@@ -3652,7 +3953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <f>data!A5</f>
         <v>45749</v>
@@ -3669,23 +3970,23 @@
         <f>C3-C2</f>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="16" t="s">
         <v>59</v>
       </c>
       <c r="K3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <f>data!A6</f>
         <v>45750</v>
@@ -3707,7 +4008,7 @@
         <v>-0.29999999999999716</v>
       </c>
       <c r="G4" s="7">
-        <f>$L$9+$M$9*F4</f>
+        <f t="shared" ref="G4:G22" si="0">$L$9+$M$9*F4</f>
         <v>-0.14255957740560693</v>
       </c>
       <c r="H4" s="7">
@@ -3717,15 +4018,15 @@
       <c r="K4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="18"/>
+      <c r="S4" s="15"/>
       <c r="U4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>data!A7</f>
         <v>45751</v>
@@ -3739,49 +4040,49 @@
         <v>58.5</v>
       </c>
       <c r="E5" s="9">
-        <f t="shared" ref="E5:E25" si="0">C5-C4</f>
+        <f t="shared" ref="E5:E25" si="1">C5-C4</f>
         <v>2</v>
       </c>
       <c r="F5" s="9">
-        <f t="shared" ref="F5:F25" si="1">E4</f>
+        <f t="shared" ref="F5:F25" si="2">E4</f>
         <v>-4</v>
       </c>
       <c r="G5" s="7">
-        <f>$L$9+$M$9*F5</f>
+        <f t="shared" si="0"/>
         <v>0.44578906296896614</v>
       </c>
       <c r="H5" s="7">
-        <f t="shared" ref="H5:H22" si="2">E5-G5</f>
+        <f t="shared" ref="H5:H22" si="3">E5-G5</f>
         <v>1.554210937031034</v>
       </c>
       <c r="I5">
         <f>H4</f>
         <v>-3.8574404225943932</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="R5" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5">
         <v>0.15894228639215383</v>
       </c>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17" t="s">
+      <c r="U5" s="14"/>
+      <c r="V5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W5" s="17" t="s">
+      <c r="W5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="X5" s="17" t="s">
+      <c r="X5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Y5" s="17" t="s">
+      <c r="Y5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="Z5" s="17" t="s">
+      <c r="Z5" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f>data!A8</f>
         <v>45755</v>
@@ -3795,54 +4096,54 @@
         <v>54.5</v>
       </c>
       <c r="E6" s="9">
+        <f t="shared" si="1"/>
+        <v>-4</v>
+      </c>
+      <c r="F6" s="9">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G6" s="7">
         <f t="shared" si="0"/>
-        <v>-4</v>
-      </c>
-      <c r="F6" s="9">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G6" s="7">
-        <f>$L$9+$M$9*F6</f>
         <v>-0.50828981331412459</v>
       </c>
       <c r="H6" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.4917101866858755</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I21" si="3">H5</f>
+        <f t="shared" ref="I6:I21" si="4">H5</f>
         <v>1.554210937031034</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="15" t="s">
+      <c r="R6" t="s">
         <v>12</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6">
         <v>2.5262650403565446E-2</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="U6" t="s">
         <v>17</v>
       </c>
-      <c r="V6" s="15">
+      <c r="V6">
         <v>1</v>
       </c>
-      <c r="W6" s="15">
+      <c r="W6">
         <v>1.6381004261960825</v>
       </c>
-      <c r="X6" s="15">
+      <c r="X6">
         <v>1.6381004261960825</v>
       </c>
-      <c r="Y6" s="15">
+      <c r="Y6">
         <v>0.41467827884547254</v>
       </c>
-      <c r="Z6" s="15">
+      <c r="Z6">
         <v>0.5287282593471323</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f>data!A9</f>
         <v>45756</v>
@@ -3856,50 +4157,48 @@
         <v>52</v>
       </c>
       <c r="E7" s="9">
+        <f t="shared" si="1"/>
+        <v>-2.5</v>
+      </c>
+      <c r="F7" s="9">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="G7" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5</v>
-      </c>
-      <c r="F7" s="9">
-        <f t="shared" si="1"/>
-        <v>-4</v>
-      </c>
-      <c r="G7" s="7">
-        <f>$L$9+$M$9*F7</f>
         <v>0.44578906296896614</v>
       </c>
       <c r="H7" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-2.945789062968966</v>
       </c>
       <c r="I7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.4917101866858755</v>
       </c>
       <c r="K7" t="s">
         <v>41</v>
       </c>
-      <c r="R7" s="15" t="s">
+      <c r="R7" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7">
         <v>-3.5658433946211709E-2</v>
       </c>
-      <c r="U7" s="15" t="s">
+      <c r="U7" t="s">
         <v>18</v>
       </c>
-      <c r="V7" s="15">
+      <c r="V7">
         <v>16</v>
       </c>
-      <c r="W7" s="15">
+      <c r="W7">
         <v>63.204677351581701</v>
       </c>
-      <c r="X7" s="15">
+      <c r="X7">
         <v>3.9502923344738563</v>
       </c>
-      <c r="Y7" s="15"/>
-      <c r="Z7" s="15"/>
-    </row>
-    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <f>data!A10</f>
         <v>45757</v>
@@ -3913,23 +4212,23 @@
         <v>55.6</v>
       </c>
       <c r="E8" s="9">
+        <f t="shared" si="1"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="F8" s="9">
+        <f t="shared" si="2"/>
+        <v>-2.5</v>
+      </c>
+      <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v>3.6000000000000014</v>
-      </c>
-      <c r="F8" s="9">
-        <f t="shared" si="1"/>
-        <v>-2.5</v>
-      </c>
-      <c r="G8" s="7">
-        <f>$L$9+$M$9*F8</f>
         <v>0.20726934389819343</v>
       </c>
       <c r="H8" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.3927306561018078</v>
       </c>
       <c r="I8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.945789062968966</v>
       </c>
       <c r="K8" t="s">
@@ -3941,26 +4240,26 @@
       <c r="M8" t="s">
         <v>56</v>
       </c>
-      <c r="R8" s="15" t="s">
+      <c r="R8" t="s">
         <v>14</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8">
         <v>1.9875342347929146</v>
       </c>
-      <c r="U8" s="16" t="s">
+      <c r="U8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="16">
+      <c r="V8" s="13">
         <v>17</v>
       </c>
-      <c r="W8" s="16">
+      <c r="W8" s="13">
         <v>64.842777777777783</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-    </row>
-    <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <f>data!A11</f>
         <v>45758</v>
@@ -3974,41 +4273,41 @@
         <v>57.5</v>
       </c>
       <c r="E9" s="9">
+        <f t="shared" si="1"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="2"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>1.8999999999999986</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="1"/>
-        <v>3.6000000000000014</v>
-      </c>
-      <c r="G9" s="7">
-        <f>$L$9+$M$9*F9</f>
         <v>-0.76271084698961567</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.6627108469896141</v>
       </c>
       <c r="I9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.3927306561018078</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="19">
         <f>S12</f>
         <v>-0.19026352121976101</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="20">
         <f>S13</f>
         <v>-0.15901314604718178</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="R9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S9" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <f>data!A12</f>
         <v>45761</v>
@@ -4022,27 +4321,27 @@
         <v>56.9</v>
       </c>
       <c r="E10" s="9">
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" si="2"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="1"/>
-        <v>1.8999999999999986</v>
-      </c>
-      <c r="G10" s="7">
-        <f>$L$9+$M$9*F10</f>
         <v>-0.49238849870940615</v>
       </c>
       <c r="H10" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.10761150129059527</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6627108469896141</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <f>data!A13</f>
         <v>45762</v>
@@ -4056,55 +4355,55 @@
         <v>56.3</v>
       </c>
       <c r="E11" s="9">
-        <f t="shared" si="0"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>-0.60000000000000142</v>
       </c>
+      <c r="F11" s="9">
+        <f t="shared" si="2"/>
+        <v>-0.60000000000000142</v>
+      </c>
       <c r="G11" s="7">
-        <f>$L$9+$M$9*F11</f>
+        <f t="shared" si="0"/>
         <v>-9.4855633591451716E-2</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.50514436640854976</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.10761150129059527</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17" t="s">
+      <c r="R11" s="14"/>
+      <c r="S11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="T11" s="17" t="s">
+      <c r="T11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="U11" s="17" t="s">
+      <c r="U11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="V11" s="17" t="s">
+      <c r="V11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="W11" s="17" t="s">
+      <c r="W11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="X11" s="17" t="s">
+      <c r="X11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="Y11" s="17" t="s">
+      <c r="Y11" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="Z11" s="17" t="s">
+      <c r="Z11" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <f>data!A14</f>
         <v>45763</v>
@@ -4118,57 +4417,57 @@
         <v>56</v>
       </c>
       <c r="E12" s="9">
+        <f t="shared" si="1"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="2"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="G12" s="7">
         <f t="shared" si="0"/>
-        <v>-0.29999999999999716</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.60000000000000142</v>
-      </c>
-      <c r="G12" s="7">
-        <f>$L$9+$M$9*F12</f>
         <v>-9.4855633591451716E-2</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.20514436640854544</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.50514436640854976</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="R12" s="15" t="s">
+      <c r="R12" t="s">
         <v>20</v>
       </c>
-      <c r="S12" s="21">
+      <c r="S12" s="7">
         <v>-0.19026352121976101</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12">
         <v>0.47064863405240476</v>
       </c>
-      <c r="U12" s="15">
+      <c r="U12">
         <v>-0.40425809713191679</v>
       </c>
-      <c r="V12" s="15">
+      <c r="V12">
         <v>0.69137527969517887</v>
       </c>
-      <c r="W12" s="15">
+      <c r="W12">
         <v>-1.1879940546186991</v>
       </c>
-      <c r="X12" s="15">
+      <c r="X12">
         <v>0.80746701217917705</v>
       </c>
-      <c r="Y12" s="15">
+      <c r="Y12">
         <v>-1.1879940546186991</v>
       </c>
-      <c r="Z12" s="15">
+      <c r="Z12">
         <v>0.80746701217917705</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <f>data!A15</f>
         <v>45764</v>
@@ -4182,54 +4481,54 @@
         <v>56</v>
       </c>
       <c r="E13" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="2"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="G13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.29999999999999716</v>
-      </c>
-      <c r="G13" s="7">
-        <f>$L$9+$M$9*F13</f>
         <v>-0.14255957740560693</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.14255957740560693</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20514436640854544</v>
       </c>
-      <c r="R13" s="16" t="s">
+      <c r="R13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="S13" s="22">
+      <c r="S13" s="18">
         <v>-0.15901314604718178</v>
       </c>
-      <c r="T13" s="16">
+      <c r="T13" s="13">
         <v>0.24693200711449162</v>
       </c>
-      <c r="U13" s="16">
+      <c r="U13" s="13">
         <v>-0.64395518387964301</v>
       </c>
-      <c r="V13" s="16">
+      <c r="V13" s="13">
         <v>0.52872825934713608</v>
       </c>
-      <c r="W13" s="16">
+      <c r="W13" s="13">
         <v>-0.68248561647653316</v>
       </c>
-      <c r="X13" s="16">
+      <c r="X13" s="13">
         <v>0.36445932438216966</v>
       </c>
-      <c r="Y13" s="16">
+      <c r="Y13" s="13">
         <v>-0.68248561647653316</v>
       </c>
-      <c r="Z13" s="16">
+      <c r="Z13" s="13">
         <v>0.36445932438216966</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f>data!A16</f>
         <v>45765</v>
@@ -4243,30 +4542,30 @@
         <v>56.6</v>
       </c>
       <c r="E14" s="9">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="F14" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
         <f t="shared" si="0"/>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="F14" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="7">
-        <f>$L$9+$M$9*F14</f>
         <v>-0.19026352121976101</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.7902635212197624</v>
       </c>
       <c r="I14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.14255957740560693</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f>data!A17</f>
         <v>45768</v>
@@ -4280,30 +4579,30 @@
         <v>56.7</v>
       </c>
       <c r="E15" s="9">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="G15" s="7">
         <f t="shared" si="0"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="F15" s="9">
-        <f t="shared" si="1"/>
-        <v>0.60000000000000142</v>
-      </c>
-      <c r="G15" s="7">
-        <f>$L$9+$M$9*F15</f>
         <v>-0.2856714088480703</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.38567140884807172</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.7902635212197624</v>
       </c>
       <c r="K15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f>data!A18</f>
         <v>45769</v>
@@ -4317,23 +4616,23 @@
         <v>56</v>
       </c>
       <c r="E16" s="9">
+        <f t="shared" si="1"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="2"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="G16" s="7">
         <f t="shared" si="0"/>
-        <v>-0.70000000000000284</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="1"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="G16" s="7">
-        <f>$L$9+$M$9*F16</f>
         <v>-0.20616483582447942</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.49383516417552342</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.38567140884807172</v>
       </c>
       <c r="K16" t="s">
@@ -4346,7 +4645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <f>data!A19</f>
         <v>45770</v>
@@ -4360,30 +4659,30 @@
         <v>56.4</v>
       </c>
       <c r="E17" s="9">
+        <f t="shared" si="1"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="F17" s="9">
+        <f t="shared" si="2"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="G17" s="7">
         <f t="shared" si="0"/>
-        <v>0.39999999999999858</v>
-      </c>
-      <c r="F17" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.70000000000000284</v>
-      </c>
-      <c r="G17" s="7">
-        <f>$L$9+$M$9*F17</f>
         <v>-7.8954318986733302E-2</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.47895431898673191</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.49383516417552342</v>
       </c>
       <c r="K17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <f>data!A20</f>
         <v>45771</v>
@@ -4397,23 +4696,23 @@
         <v>56.3</v>
       </c>
       <c r="E18" s="9">
+        <f t="shared" si="1"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="2"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="G18" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10000000000000142</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" si="1"/>
-        <v>0.39999999999999858</v>
-      </c>
-      <c r="G18" s="7">
-        <f>$L$9+$M$9*F18</f>
         <v>-0.25386877963863352</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1538687796386321</v>
       </c>
       <c r="I18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.47895431898673191</v>
       </c>
       <c r="K18" t="s">
@@ -4425,15 +4724,15 @@
       <c r="M18" t="s">
         <v>58</v>
       </c>
-      <c r="R18" s="18" t="s">
+      <c r="R18" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="S18" s="18"/>
+      <c r="S18" s="15"/>
       <c r="U18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <f>data!A21</f>
         <v>45772</v>
@@ -4447,57 +4746,57 @@
         <v>58.3</v>
       </c>
       <c r="E19" s="9">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="2"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="G19" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="F19" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.10000000000000142</v>
-      </c>
-      <c r="G19" s="7">
-        <f>$L$9+$M$9*F19</f>
         <v>-0.17436220661504259</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.1743622066150428</v>
       </c>
       <c r="I19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.1538687796386321</v>
       </c>
-      <c r="L19" s="25">
+      <c r="L19" s="21">
         <f>S26</f>
         <v>0.22652862003091939</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="22">
         <f>S27</f>
         <v>-3.9581497398492753E-2</v>
       </c>
-      <c r="R19" s="15" t="s">
+      <c r="R19" t="s">
         <v>11</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19">
         <v>4.567242436591519E-2</v>
       </c>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17" t="s">
+      <c r="U19" s="14"/>
+      <c r="V19" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="17" t="s">
+      <c r="W19" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="X19" s="17" t="s">
+      <c r="X19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Y19" s="17" t="s">
+      <c r="Y19" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="Z19" s="17" t="s">
+      <c r="Z19" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f>data!A22</f>
         <v>45775</v>
@@ -4511,51 +4810,51 @@
         <v>57.5</v>
       </c>
       <c r="E20" s="9">
+        <f t="shared" si="1"/>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="7">
         <f t="shared" si="0"/>
-        <v>-0.79999999999999716</v>
-      </c>
-      <c r="F20" s="9">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G20" s="7">
-        <f>$L$9+$M$9*F20</f>
         <v>-0.50828981331412459</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.29171018668587256</v>
       </c>
       <c r="I20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1743622066150428</v>
       </c>
-      <c r="R20" s="15" t="s">
+      <c r="R20" t="s">
         <v>12</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20">
         <v>2.0859703474602437E-3</v>
       </c>
-      <c r="U20" s="15" t="s">
+      <c r="U20" t="s">
         <v>17</v>
       </c>
-      <c r="V20" s="15">
+      <c r="V20">
         <v>1</v>
       </c>
-      <c r="W20" s="15">
+      <c r="W20">
         <v>9.8978345211307328E-2</v>
       </c>
-      <c r="X20" s="15">
+      <c r="X20">
         <v>9.8978345211307328E-2</v>
       </c>
-      <c r="Y20" s="15">
+      <c r="Y20">
         <v>3.1354960730232702E-2</v>
       </c>
-      <c r="Z20" s="15">
+      <c r="Z20">
         <v>0.86181963605752743</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f>data!A23</f>
         <v>45776</v>
@@ -4569,246 +4868,244 @@
         <v>57.6</v>
       </c>
       <c r="E21" s="9">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="2"/>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="G21" s="7">
         <f t="shared" si="0"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="F21" s="9">
-        <f t="shared" si="1"/>
-        <v>-0.79999999999999716</v>
-      </c>
-      <c r="G21" s="7">
-        <f>$L$9+$M$9*F21</f>
         <v>-6.3053004382016026E-2</v>
       </c>
       <c r="H21" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.16305300438201745</v>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.29171018668587256</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R21" s="15" t="s">
+      <c r="R21" t="s">
         <v>13</v>
       </c>
-      <c r="S21" s="15">
+      <c r="S21">
         <v>-6.4441631629375745E-2</v>
       </c>
-      <c r="U21" s="15" t="s">
+      <c r="U21" t="s">
         <v>18</v>
       </c>
-      <c r="V21" s="15">
+      <c r="V21">
         <v>15</v>
       </c>
-      <c r="W21" s="15">
+      <c r="W21">
         <v>47.35056729757197</v>
       </c>
-      <c r="X21" s="15">
+      <c r="X21">
         <v>3.1567044865047982</v>
       </c>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-    </row>
-    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="31">
+    </row>
+    <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="27">
         <f>B21+1</f>
         <v>21</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="28">
         <f>$L$22+$M$9*E21+$M$19*H21</f>
         <v>56.802644803326523</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29">
+      <c r="D22" s="24"/>
+      <c r="E22" s="25">
+        <f t="shared" si="1"/>
+        <v>-0.79735519667347887</v>
+      </c>
+      <c r="F22" s="26">
+        <f t="shared" si="2"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="G22" s="26">
         <f t="shared" si="0"/>
-        <v>-0.79735519667347887</v>
-      </c>
-      <c r="F22" s="30">
-        <f t="shared" si="1"/>
-        <v>0.10000000000000142</v>
-      </c>
-      <c r="G22" s="30">
-        <f>$L$9+$M$9*F22</f>
         <v>-0.20616483582447942</v>
       </c>
-      <c r="H22" s="30">
-        <f t="shared" si="2"/>
+      <c r="H22" s="26">
+        <f t="shared" si="3"/>
         <v>-0.59119036084899945</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L22" s="27">
+      <c r="L22" s="23">
         <f>AVERAGE(C2:D21)</f>
         <v>56.825000000000003</v>
       </c>
-      <c r="R22" s="15" t="s">
+      <c r="R22" t="s">
         <v>14</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22">
         <v>1.7767117060752422</v>
       </c>
-      <c r="U22" s="16" t="s">
+      <c r="U22" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="V22" s="16">
+      <c r="V22" s="13">
         <v>16</v>
       </c>
-      <c r="W22" s="16">
+      <c r="W22" s="13">
         <v>47.449545642783278</v>
       </c>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-    </row>
-    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="31">
-        <f t="shared" ref="B23:B25" si="4">B22+1</f>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="13"/>
+    </row>
+    <row r="23" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="27">
+        <f t="shared" ref="B23:B25" si="5">B22+1</f>
         <v>22</v>
       </c>
-      <c r="C23" s="32">
-        <f t="shared" ref="C23:C25" si="5">$L$22+$M$9*E22+$M$19*H22</f>
+      <c r="C23" s="28">
+        <f t="shared" ref="C23:C25" si="6">$L$22+$M$9*E22+$M$19*H22</f>
         <v>56.975190158070077</v>
       </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="29">
-        <f t="shared" si="0"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="25">
+        <f t="shared" si="1"/>
         <v>0.17254535474355492</v>
       </c>
-      <c r="F23" s="30">
-        <f t="shared" si="1"/>
+      <c r="F23" s="26">
+        <f t="shared" si="2"/>
         <v>-0.79735519667347887</v>
       </c>
-      <c r="G23" s="30">
-        <f t="shared" ref="G23:G25" si="6">$L$9+$M$9*F23</f>
+      <c r="G23" s="26">
+        <f t="shared" ref="G23:G25" si="7">$L$9+$M$9*F23</f>
         <v>-6.3473562879641759E-2</v>
       </c>
-      <c r="H23" s="30">
-        <f t="shared" ref="H23:H25" si="7">E23-G23</f>
+      <c r="H23" s="26">
+        <f t="shared" ref="H23:H25" si="8">E23-G23</f>
         <v>0.23601891762319668</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R23" s="16" t="s">
+      <c r="R23" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="S23" s="16">
+      <c r="S23" s="13">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="31">
-        <f t="shared" si="4"/>
+    <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="27">
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="C24" s="32">
-        <f t="shared" si="5"/>
+      <c r="C24" s="28">
+        <f t="shared" si="6"/>
         <v>56.788221038132505</v>
       </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.18696911993757226</v>
-      </c>
-      <c r="F24" s="30">
-        <f t="shared" si="1"/>
-        <v>0.17254535474355492</v>
-      </c>
-      <c r="G24" s="30">
-        <f t="shared" si="6"/>
-        <v>-0.21770050091336068</v>
-      </c>
-      <c r="H24" s="30">
-        <f t="shared" si="7"/>
-        <v>3.0731380975788425E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B25" s="31">
-        <f t="shared" si="4"/>
-        <v>24</v>
-      </c>
-      <c r="C25" s="32">
-        <f t="shared" si="5"/>
-        <v>56.853514153898807</v>
-      </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="29">
-        <f t="shared" si="0"/>
-        <v>6.5293115766301923E-2</v>
-      </c>
-      <c r="F25" s="30">
+      <c r="D24" s="24"/>
+      <c r="E24" s="25">
         <f t="shared" si="1"/>
         <v>-0.18696911993757226</v>
       </c>
-      <c r="G25" s="30">
+      <c r="F24" s="26">
+        <f t="shared" si="2"/>
+        <v>0.17254535474355492</v>
+      </c>
+      <c r="G24" s="26">
+        <f t="shared" si="7"/>
+        <v>-0.21770050091336068</v>
+      </c>
+      <c r="H24" s="26">
+        <f t="shared" si="8"/>
+        <v>3.0731380975788425E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B25" s="27">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="C25" s="28">
         <f t="shared" si="6"/>
+        <v>56.853514153898807</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25">
+        <f t="shared" si="1"/>
+        <v>6.5293115766301923E-2</v>
+      </c>
+      <c r="F25" s="26">
+        <f t="shared" si="2"/>
+        <v>-0.18696911993757226</v>
+      </c>
+      <c r="G25" s="26">
+        <f t="shared" si="7"/>
         <v>-0.16053297324481478</v>
       </c>
-      <c r="H25" s="30">
-        <f t="shared" si="7"/>
+      <c r="H25" s="26">
+        <f t="shared" si="8"/>
         <v>0.2258260890111167</v>
       </c>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17" t="s">
+      <c r="R25" s="14"/>
+      <c r="S25" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="T25" s="17" t="s">
+      <c r="T25" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="U25" s="17" t="s">
+      <c r="U25" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="V25" s="17" t="s">
+      <c r="V25" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="W25" s="17" t="s">
+      <c r="W25" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="X25" s="17" t="s">
+      <c r="X25" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="Y25" s="17" t="s">
+      <c r="Y25" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="Z25" s="17" t="s">
+      <c r="Z25" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="R26" s="15" t="s">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="R26" t="s">
         <v>20</v>
       </c>
-      <c r="S26" s="21">
+      <c r="S26" s="7">
         <v>0.22652862003091939</v>
       </c>
-      <c r="T26" s="15">
+      <c r="T26">
         <v>0.4309212176479883</v>
       </c>
-      <c r="U26" s="15">
+      <c r="U26">
         <v>0.5256845352552737</v>
       </c>
-      <c r="V26" s="15">
+      <c r="V26">
         <v>0.60679213900757478</v>
       </c>
-      <c r="W26" s="15">
+      <c r="W26">
         <v>-0.69195821349694975</v>
       </c>
-      <c r="X26" s="15">
+      <c r="X26">
         <v>1.1450154535587886</v>
       </c>
-      <c r="Y26" s="15">
+      <c r="Y26">
         <v>-0.69195821349694975</v>
       </c>
-      <c r="Z26" s="15">
+      <c r="Z26">
         <v>1.1450154535587886</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>45776</v>
       </c>
@@ -4829,35 +5126,35 @@
         <f>E27-G27</f>
         <v>5.8780000000000589E-2</v>
       </c>
-      <c r="R27" s="16" t="s">
+      <c r="R27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="S27" s="22">
+      <c r="S27" s="18">
         <v>-3.9581497398492753E-2</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="13">
         <v>0.22353168366373413</v>
       </c>
-      <c r="U27" s="16">
+      <c r="U27" s="13">
         <v>-0.17707332021010708</v>
       </c>
-      <c r="V27" s="16">
+      <c r="V27" s="13">
         <v>0.86181963605753087</v>
       </c>
-      <c r="W27" s="16">
+      <c r="W27" s="13">
         <v>-0.51602800296177009</v>
       </c>
-      <c r="X27" s="16">
+      <c r="X27" s="13">
         <v>0.43686500816478457</v>
       </c>
-      <c r="Y27" s="16">
+      <c r="Y27" s="13">
         <v>-0.51602800296177009</v>
       </c>
-      <c r="Z27" s="16">
+      <c r="Z27" s="13">
         <v>0.43686500816478457</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C28" s="9">
         <f>C27+E28</f>
         <v>57.58246939</v>
@@ -4867,22 +5164,22 @@
         <v>-1.7530610000000175E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="K30" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="K31" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L35" s="7">
         <v>0.41220000000000001</v>
       </c>
     </row>
-    <row r="36" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L36" s="7">
         <v>-0.99950000000000006</v>
       </c>
@@ -4895,4 +5192,1227 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EF7BBE-535E-4830-9D87-8C3F074145AE}">
+  <dimension ref="A1:V28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>data!C4</f>
+        <v>60.8</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>data!C5</f>
+        <v>60.5</v>
+      </c>
+      <c r="C3">
+        <f>B2</f>
+        <v>60.8</v>
+      </c>
+      <c r="D3">
+        <f>B3-C3</f>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>data!C6</f>
+        <v>56.5</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C21" si="0">B3</f>
+        <v>60.5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D21" si="1">B4-C4</f>
+        <v>-4</v>
+      </c>
+      <c r="E4">
+        <f>D3</f>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="F4">
+        <f>$K$4+$L$4*E4</f>
+        <v>-0.16126785301198651</v>
+      </c>
+      <c r="G4">
+        <f>D4-F4</f>
+        <v>-3.8387321469880136</v>
+      </c>
+      <c r="K4">
+        <f>O12</f>
+        <v>-0.20892929050609582</v>
+      </c>
+      <c r="L4">
+        <f>O13</f>
+        <v>-0.15887145831369923</v>
+      </c>
+      <c r="N4" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="34"/>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>data!C7</f>
+        <v>58.5</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>56.5</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E26" si="2">D4</f>
+        <v>-4</v>
+      </c>
+      <c r="F5">
+        <f>$K$4+$L$4*E5</f>
+        <v>0.42655654274870108</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G5:G21" si="3">D5-F5</f>
+        <v>1.573443457251299</v>
+      </c>
+      <c r="H5">
+        <f>G4</f>
+        <v>-3.8387321469880136</v>
+      </c>
+      <c r="N5" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="31">
+        <v>0.15894228639215272</v>
+      </c>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>data!C8</f>
+        <v>54.5</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>58.5</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>-4</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <f>$K$4+$L$4*E6</f>
+        <v>-0.52667220713349427</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="3"/>
+        <v>-3.4733277928665056</v>
+      </c>
+      <c r="H6">
+        <f t="shared" ref="H6:H26" si="4">G5</f>
+        <v>1.573443457251299</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="31">
+        <v>2.5262650403565096E-2</v>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="R6" s="31">
+        <v>1</v>
+      </c>
+      <c r="S6" s="31">
+        <v>1.6366408063949649</v>
+      </c>
+      <c r="T6" s="31">
+        <v>1.6366408063949649</v>
+      </c>
+      <c r="U6" s="31">
+        <v>0.4146782788454666</v>
+      </c>
+      <c r="V6" s="31">
+        <v>0.52872825934713541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>data!C9</f>
+        <v>52</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>54.5</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>-2.5</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="F7">
+        <f>$K$4+$L$4*E7</f>
+        <v>0.42655654274870108</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="3"/>
+        <v>-2.9265565427487013</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="4"/>
+        <v>-3.4733277928665056</v>
+      </c>
+      <c r="K7" s="6">
+        <f>O27</f>
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="L7" s="6">
+        <f>O28</f>
+        <v>-3.9694620343556128E-2</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" s="31">
+        <v>-3.5658433946212084E-2</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="31">
+        <v>16</v>
+      </c>
+      <c r="S7" s="31">
+        <v>63.148359193605046</v>
+      </c>
+      <c r="T7" s="31">
+        <v>3.9467724496003154</v>
+      </c>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>data!C10</f>
+        <v>55.6</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>-2.5</v>
+      </c>
+      <c r="F8">
+        <f>$K$4+$L$4*E8</f>
+        <v>0.18824935527815223</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="3"/>
+        <v>3.4117506447218493</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="4"/>
+        <v>-2.9265565427487013</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="O8" s="31">
+        <v>1.9866485470762854</v>
+      </c>
+      <c r="Q8" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" s="32">
+        <v>17</v>
+      </c>
+      <c r="S8" s="32">
+        <v>64.785000000000011</v>
+      </c>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f>data!C11</f>
+        <v>57.5</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>55.6</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>3.6000000000000014</v>
+      </c>
+      <c r="F9">
+        <f>$K$4+$L$4*E9</f>
+        <v>-0.78086654043541337</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="3"/>
+        <v>2.6808665404354119</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="4"/>
+        <v>3.4117506447218493</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" s="32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f>data!C12</f>
+        <v>56.9</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>57.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>1.8999999999999986</v>
+      </c>
+      <c r="F10">
+        <f>$K$4+$L$4*E10</f>
+        <v>-0.51078506130212409</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="3"/>
+        <v>-8.9214938697877333E-2</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="4"/>
+        <v>2.6808665404354119</v>
+      </c>
+      <c r="J10" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="37"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f>data!C13</f>
+        <v>56.3</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>56.9</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F11">
+        <f>$K$4+$L$4*E11</f>
+        <v>-0.11360641551787606</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="3"/>
+        <v>-0.48639358448212533</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="4"/>
+        <v>-8.9214938697877333E-2</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="S11" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="T11" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U11" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="V11" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f>data!C14</f>
+        <v>56</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>56.3</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>-0.60000000000000142</v>
+      </c>
+      <c r="F12">
+        <f>$K$4+$L$4*E12</f>
+        <v>-0.11360641551787606</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="3"/>
+        <v>-0.18639358448212109</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="4"/>
+        <v>-0.48639358448212533</v>
+      </c>
+      <c r="N12" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="35">
+        <v>-0.20892929050609582</v>
+      </c>
+      <c r="P12" s="31">
+        <v>0.46994153132839239</v>
+      </c>
+      <c r="Q12" s="31">
+        <v>-0.44458571243003686</v>
+      </c>
+      <c r="R12" s="31">
+        <v>0.66257420696150149</v>
+      </c>
+      <c r="S12" s="31">
+        <v>-1.2051608330933063</v>
+      </c>
+      <c r="T12" s="31">
+        <v>0.7873022520811146</v>
+      </c>
+      <c r="U12" s="31">
+        <v>-1.2051608330933063</v>
+      </c>
+      <c r="V12" s="31">
+        <v>0.7873022520811146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f>data!C15</f>
+        <v>56</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="F13">
+        <f>$K$4+$L$4*E13</f>
+        <v>-0.16126785301198651</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>0.16126785301198651</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="4"/>
+        <v>-0.18639358448212109</v>
+      </c>
+      <c r="N13" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="36">
+        <v>-0.15887145831369923</v>
+      </c>
+      <c r="P13" s="32">
+        <v>0.24671197979422213</v>
+      </c>
+      <c r="Q13" s="32">
+        <v>-0.64395518387964357</v>
+      </c>
+      <c r="R13" s="32">
+        <v>0.52872825934713574</v>
+      </c>
+      <c r="S13" s="32">
+        <v>-0.68187749166083789</v>
+      </c>
+      <c r="T13" s="32">
+        <v>0.36413457503343949</v>
+      </c>
+      <c r="U13" s="32">
+        <v>-0.68187749166083789</v>
+      </c>
+      <c r="V13" s="32">
+        <v>0.36413457503343949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <f>data!C16</f>
+        <v>56.6</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>$K$4+$L$4*E14</f>
+        <v>-0.20892929050609582</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>0.80892929050609719</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="4"/>
+        <v>0.16126785301198651</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <f>data!C17</f>
+        <v>56.7</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>56.6</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>0.60000000000000142</v>
+      </c>
+      <c r="F15">
+        <f>$K$4+$L$4*E15</f>
+        <v>-0.30425216549431555</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>0.40425216549431697</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="4"/>
+        <v>0.80892929050609719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <f>data!C18</f>
+        <v>56</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>56.7</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F16">
+        <f>$K$4+$L$4*E16</f>
+        <v>-0.22481643633746598</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="3"/>
+        <v>-0.47518356366253689</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="4"/>
+        <v>0.40425216549431697</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <f>data!C19</f>
+        <v>56.4</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="F17">
+        <f>$K$4+$L$4*E17</f>
+        <v>-9.7719269686505905E-2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>0.49771926968650448</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="4"/>
+        <v>-0.47518356366253689</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <f>data!C20</f>
+        <v>56.3</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>56.4</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="F18">
+        <f>$K$4+$L$4*E18</f>
+        <v>-0.27247787383157529</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="3"/>
+        <v>0.17247787383157387</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="4"/>
+        <v>0.49771926968650448</v>
+      </c>
+      <c r="N18" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="34"/>
+      <c r="Q18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <f>data!C21</f>
+        <v>58.3</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>56.3</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="F19">
+        <f>$K$4+$L$4*E19</f>
+        <v>-0.19304214467472566</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>2.1930421446747257</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="4"/>
+        <v>0.17247787383157387</v>
+      </c>
+      <c r="N19" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="O19" s="31">
+        <v>4.5802878762687585E-2</v>
+      </c>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="T19" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="V19" s="33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <f>data!C22</f>
+        <v>57.5</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>58.3</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <f>$K$4+$L$4*E20</f>
+        <v>-0.52667220713349427</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>-0.27332779286650288</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="4"/>
+        <v>2.1930421446747257</v>
+      </c>
+      <c r="N20" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="31">
+        <v>2.0979037029494572E-3</v>
+      </c>
+      <c r="Q20" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="R20" s="31">
+        <v>1</v>
+      </c>
+      <c r="S20" s="31">
+        <v>9.9544863516129567E-2</v>
+      </c>
+      <c r="T20" s="31">
+        <v>9.9544863516129567E-2</v>
+      </c>
+      <c r="U20" s="31">
+        <v>3.1534712334018847E-2</v>
+      </c>
+      <c r="V20" s="31">
+        <v>0.86142852511386536</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <f>data!C23</f>
+        <v>57.6</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>57.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="F21">
+        <f>$K$4+$L$4*E21</f>
+        <v>-8.1832123855136885E-2</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>0.18183212385513831</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="4"/>
+        <v>-0.27332779286650288</v>
+      </c>
+      <c r="N21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="O21" s="31">
+        <v>-6.4428902716853906E-2</v>
+      </c>
+      <c r="Q21" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="R21" s="31">
+        <v>15</v>
+      </c>
+      <c r="S21" s="31">
+        <v>47.350137110055279</v>
+      </c>
+      <c r="T21" s="31">
+        <v>3.1566758073370185</v>
+      </c>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
+    </row>
+    <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="40">
+        <f>B21+D22</f>
+        <v>57.613925872292128</v>
+      </c>
+      <c r="D22" s="39">
+        <f>$K$4+$L$4*D21+$K$7+L7*G21</f>
+        <v>1.392587229212346E-2</v>
+      </c>
+      <c r="E22" s="39">
+        <f t="shared" si="2"/>
+        <v>0.10000000000000142</v>
+      </c>
+      <c r="F22" s="39">
+        <f t="shared" ref="F22:F26" si="5">$K$4+$L$4*E22</f>
+        <v>-0.22481643633746598</v>
+      </c>
+      <c r="G22" s="39">
+        <f t="shared" ref="G22:G25" si="6">D22-F22</f>
+        <v>0.23874230862958945</v>
+      </c>
+      <c r="H22" s="39">
+        <f t="shared" si="4"/>
+        <v>0.18183212385513831</v>
+      </c>
+      <c r="N22" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="31">
+        <v>1.7767036352011605</v>
+      </c>
+      <c r="Q22" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" s="32">
+        <v>16</v>
+      </c>
+      <c r="S22" s="32">
+        <v>47.449681973571408</v>
+      </c>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+    </row>
+    <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="40">
+        <f t="shared" ref="B23:B25" si="7">B22+D23</f>
+        <v>57.648744223898973</v>
+      </c>
+      <c r="D23" s="39">
+        <f t="shared" ref="D23:D25" si="8">$K$4+$L$4*D22+$K$7+L8*G22</f>
+        <v>3.4818351606845821E-2</v>
+      </c>
+      <c r="E23" s="39">
+        <f t="shared" si="2"/>
+        <v>1.392587229212346E-2</v>
+      </c>
+      <c r="F23" s="39">
+        <f t="shared" si="5"/>
+        <v>-0.21114171414543581</v>
+      </c>
+      <c r="G23" s="39">
+        <f t="shared" si="6"/>
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="H23" s="39">
+        <f t="shared" si="4"/>
+        <v>0.23874230862958945</v>
+      </c>
+      <c r="N23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="O23" s="32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="40">
+        <f t="shared" si="7"/>
+        <v>57.680243356849303</v>
+      </c>
+      <c r="D24" s="39">
+        <f t="shared" si="8"/>
+        <v>3.149913295032708E-2</v>
+      </c>
+      <c r="E24" s="39">
+        <f t="shared" si="2"/>
+        <v>3.4818351606845821E-2</v>
+      </c>
+      <c r="F24" s="39">
+        <f t="shared" si="5"/>
+        <v>-0.21446093280195455</v>
+      </c>
+      <c r="G24" s="39">
+        <f t="shared" si="6"/>
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="H24" s="39">
+        <f t="shared" si="4"/>
+        <v>0.24596006575228163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="40">
+        <f t="shared" si="7"/>
+        <v>57.712269818908055</v>
+      </c>
+      <c r="D25" s="39">
+        <f t="shared" si="8"/>
+        <v>3.202646205875026E-2</v>
+      </c>
+      <c r="E25" s="39">
+        <f t="shared" si="2"/>
+        <v>3.149913295032708E-2</v>
+      </c>
+      <c r="F25" s="39">
+        <f t="shared" si="5"/>
+        <v>-0.21393360369353137</v>
+      </c>
+      <c r="G25" s="39">
+        <f t="shared" si="6"/>
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="H25" s="39">
+        <f t="shared" si="4"/>
+        <v>0.24596006575228163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="40">
+        <f>B25+D26</f>
+        <v>57.744212503422339</v>
+      </c>
+      <c r="D26" s="39">
+        <f>$K$4+$L$4*D25+$K$7+L11*G25</f>
+        <v>3.1942684514283809E-2</v>
+      </c>
+      <c r="E26" s="39">
+        <f t="shared" si="2"/>
+        <v>3.202646205875026E-2</v>
+      </c>
+      <c r="F26" s="39">
+        <f t="shared" si="5"/>
+        <v>-0.21401738123799782</v>
+      </c>
+      <c r="G26" s="39">
+        <f t="shared" ref="G26" si="9">D26-F26</f>
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="H26" s="39">
+        <f t="shared" si="4"/>
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R26" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="S26" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="T26" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U26" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="V26" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="N27" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="35">
+        <v>0.24596006575228163</v>
+      </c>
+      <c r="P27" s="31">
+        <v>0.43091872268812187</v>
+      </c>
+      <c r="Q27" s="31">
+        <v>0.57078064331471534</v>
+      </c>
+      <c r="R27" s="31">
+        <v>0.57660005881820742</v>
+      </c>
+      <c r="S27" s="31">
+        <v>-0.67252144989451401</v>
+      </c>
+      <c r="T27" s="31">
+        <v>1.1644415813990774</v>
+      </c>
+      <c r="U27" s="31">
+        <v>-0.67252144989451401</v>
+      </c>
+      <c r="V27" s="31">
+        <v>1.1644415813990774</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N28" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="O28" s="36">
+        <v>-3.9694620343556128E-2</v>
+      </c>
+      <c r="P28" s="32">
+        <v>0.22353071933661189</v>
+      </c>
+      <c r="Q28" s="32">
+        <v>-0.17758015748958664</v>
+      </c>
+      <c r="R28" s="32">
+        <v>0.86142852511384893</v>
+      </c>
+      <c r="S28" s="32">
+        <v>-0.51613907049222696</v>
+      </c>
+      <c r="T28" s="32">
+        <v>0.43674982980511473</v>
+      </c>
+      <c r="U28" s="32">
+        <v>-0.51613907049222696</v>
+      </c>
+      <c r="V28" s="32">
+        <v>0.43674982980511473</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>